--- a/bench-container-v2/ig/StructureDefinition-cds-organization.xlsx
+++ b/bench-container-v2/ig/StructureDefinition-cds-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:26:37+00:00</t>
+    <t>2026-06-25T15:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/bench-container-v2/ig/StructureDefinition-cds-organization.xlsx
+++ b/bench-container-v2/ig/StructureDefinition-cds-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:33:54+00:00</t>
+    <t>2026-06-25T15:48:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
